--- a/artfynd/A 1720-2024 artfynd.xlsx
+++ b/artfynd/A 1720-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1720-2024 artfynd.xlsx
+++ b/artfynd/A 1720-2024 artfynd.xlsx
@@ -790,12 +790,7 @@
         <v>74119899</v>
       </c>
       <c r="B3" t="n">
-        <v>103226</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499180.8515191179</v>
+        <v>499181</v>
       </c>
       <c r="R3" t="n">
-        <v>6435612.354717387</v>
+        <v>6435612</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -860,19 +855,9 @@
           <t>1981-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 1720-2024 artfynd.xlsx
+++ b/artfynd/A 1720-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>74119899</v>
       </c>
       <c r="B3" t="n">
-        <v>105603</v>
+        <v>105612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1720-2024 artfynd.xlsx
+++ b/artfynd/A 1720-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>74119899</v>
       </c>
       <c r="B3" t="n">
-        <v>105612</v>
+        <v>105615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1720-2024 artfynd.xlsx
+++ b/artfynd/A 1720-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>74119899</v>
       </c>
       <c r="B3" t="n">
-        <v>105615</v>
+        <v>105643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1720-2024 artfynd.xlsx
+++ b/artfynd/A 1720-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>74119899</v>
       </c>
       <c r="B3" t="n">
-        <v>105643</v>
+        <v>105649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1720-2024 artfynd.xlsx
+++ b/artfynd/A 1720-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>74119899</v>
       </c>
       <c r="B3" t="n">
-        <v>105649</v>
+        <v>105656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1720-2024 artfynd.xlsx
+++ b/artfynd/A 1720-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>74119899</v>
       </c>
       <c r="B3" t="n">
-        <v>105656</v>
+        <v>105660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1720-2024 artfynd.xlsx
+++ b/artfynd/A 1720-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>74119899</v>
       </c>
       <c r="B3" t="n">
-        <v>105660</v>
+        <v>105667</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1720-2024 artfynd.xlsx
+++ b/artfynd/A 1720-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>74119899</v>
       </c>
       <c r="B3" t="n">
-        <v>105670</v>
+        <v>105675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1720-2024 artfynd.xlsx
+++ b/artfynd/A 1720-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>74119899</v>
       </c>
       <c r="B3" t="n">
-        <v>105675</v>
+        <v>105683</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1720-2024 artfynd.xlsx
+++ b/artfynd/A 1720-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>74119899</v>
       </c>
       <c r="B3" t="n">
-        <v>105683</v>
+        <v>105693</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1720-2024 artfynd.xlsx
+++ b/artfynd/A 1720-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133055</v>
+        <v>74119899</v>
       </c>
       <c r="B2" t="n">
-        <v>103225</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106204</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -711,17 +706,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>F-Tra-106, Sm</t>
+          <t>Trappan 700 m O, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499186.1532901581</v>
+        <v>499181</v>
       </c>
       <c r="R2" t="n">
-        <v>6435617.644339496</v>
+        <v>6435612</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,26 +740,21 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1981-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1984-12-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7F7a 2816. SOM: Chimaphila umbellata. LEG: Karin Tilander, Kjell Rönning</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -775,117 +765,15 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lennart Ring</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lennart Ring</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>74119899</v>
-      </c>
-      <c r="B3" t="n">
-        <v>105693</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>340</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Ryl</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Chimaphila umbellata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Trappan 700 m O, Sm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>499181</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6435612</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Tranås</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Tranås</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>1981-01-01</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 7F7a 2816. SOM: Chimaphila umbellata. LEG: Karin Tilander, Kjell Rönning</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 1720-2024 artfynd.xlsx
+++ b/artfynd/A 1720-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,8 +783,16 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74119899</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>